--- a/Data/evaluation/query_responses.xlsx
+++ b/Data/evaluation/query_responses.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C338"/>
+  <dimension ref="A1:C339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -434,17 +422,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
@@ -6342,6 +6330,25 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>What are the steps taken to import qualitative data?</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>llama3.2:latest</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Option 1: SelectTrackSettings from the Edit menu, then select Import from File, browse to the .txt file, select it and Open, and click OK to exit Qualitative Track Information.
+Option 2: SelectTrackSettings from the Edit menu, then select Details on the qualitative track, select Import from File, browse to the .txt file, select it and Open, and click OK to exit Qualitative Track Information.
+Option 3: SelectTrackSettings from the Edit menu, then select Export to File or Export to Clipboard, select the desired export option, browse to the location or external application, enter a file name if exporting to file, and paste the contents of the clipboard if exporting to clipboard.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/evaluation/query_responses.xlsx
+++ b/Data/evaluation/query_responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C339"/>
+  <dimension ref="A1:C340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -6349,6 +6349,25 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>What are the steps taken to import qualitative data?</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>llama3.2:latest</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Option 1: SelectTrackSettings, then selectImport from File, browse to the .txt file, select it and Open, and click OK to exit Qualitative Track Information.
+Option 2: SelectTrackSettings, then select the qualitative track, selectDetails, selectImport from File, browse to the .txt file, select it and Open, and click OK to exit Qualitative Track Information.
+Option 3: SelectTrackSettings, then select the qualitative track you wish to export data from, selectDetails, Export to File, save the file in a location of your choice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/evaluation/query_responses.xlsx
+++ b/Data/evaluation/query_responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C340"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -6368,6 +6368,25 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>What are the limits of GIS fields in GEO?</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>llama3.2:latest</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Option 1: No specific limit is mentioned for GIS fields in the provided documents.
+Option 2: The provided documents do not mention any limits for GIS fields.
+Option 3: There is no information available on limits for GIS fields within GEO.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/evaluation/query_responses.xlsx
+++ b/Data/evaluation/query_responses.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C341"/>
+  <dimension ref="A1:C343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -6387,6 +6387,44 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>How do I import qualitative data into GEO?</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>llama3.2:latest</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Option 1: Export to File; select Export to File, browse to a location, enter a file name, and select Save.
+Option 2: Export to Clipboard; select Export to Clipboard, open an external application (i.e. Excel), paste the contents of your clipboard.
+Option 3: Import from File; select Import from File, browse to the .txt file, select it, and Open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>What are the limits of GIS fields in GEO?</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>llama3.2:latest</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Option 1: No specific limit is mentioned for GIS fields in the provided documents.
+Option 2: The provided documents do not mention any limits for GIS fields.
+Option 3: There is no information available on limits for GIS fields within GEO.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
